--- a/settlement/Inequality Input Data Template CMCC Settlement EMPTY.xlsx
+++ b/settlement/Inequality Input Data Template CMCC Settlement EMPTY.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emmerling\CMCC Dropbox\Johannes Emmerling\EIEE\NAVIGATE\NAVIGATE-RESEARCH\WP4 Inequality\inequality-dataset-for-iams\settlement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D522F1C-B82F-455C-91BD-FC9C0E1373F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7844487-D14E-43C9-98F3-D93AE23E67FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7B1F585D-5655-48D5-9EC0-02F8EFD3D86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Inequality Input Data Template " sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="77">
   <si>
     <t>MODEL</t>
   </si>
@@ -239,13 +252,25 @@
   </si>
   <si>
     <t>Digital Access|Electric Grid|Rural|Dx</t>
+  </si>
+  <si>
+    <t>Expenditure Share|Urban</t>
+  </si>
+  <si>
+    <t>Share of TOTAL Expenditures of Urban Households</t>
+  </si>
+  <si>
+    <t>Expenditure Share|Rural</t>
+  </si>
+  <si>
+    <t>Share of TOTAL Expenditures of Rural Households</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +401,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -722,8 +754,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1099,8 +1132,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DA951D2-50BA-4D44-A188-00AF4DB0B195}">
-  <dimension ref="A1:AO51"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="36.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1283,18 +1319,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
+    <row r="6" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.35">
@@ -1302,7 +1338,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1316,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1327,10 +1363,10 @@
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1341,10 +1377,10 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1355,24 +1391,24 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1386,7 +1422,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1400,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1414,7 +1450,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1428,10 +1464,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1439,24 +1478,21 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1464,13 +1500,13 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1478,13 +1514,13 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1492,27 +1528,27 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1520,13 +1556,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1534,13 +1570,13 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1548,13 +1584,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1562,27 +1598,27 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1590,7 +1626,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1601,10 +1637,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1618,7 +1654,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1632,13 +1668,13 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1646,21 +1682,21 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -1674,7 +1710,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -1688,7 +1724,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -1702,10 +1738,13 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -1713,38 +1752,35 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -1752,13 +1788,13 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -1766,70 +1802,82 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="F42" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="E45" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
         <v>65</v>
       </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
         <v>66</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D46" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D47" t="s">
-        <v>68</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -1837,7 +1885,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -1845,7 +1893,7 @@
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -1853,7 +1901,7 @@
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -1861,9 +1909,25 @@
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D52" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D53" t="s">
         <v>72</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E53" t="s">
         <v>8</v>
       </c>
     </row>

--- a/settlement/Inequality Input Data Template CMCC Settlement EMPTY.xlsx
+++ b/settlement/Inequality Input Data Template CMCC Settlement EMPTY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emmerling\CMCC Dropbox\Johannes Emmerling\EIEE\NAVIGATE\NAVIGATE-RESEARCH\WP4 Inequality\inequality-dataset-for-iams\settlement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\PRISMA\7.Work packages\WP2\inequality-dataset-for-iams\settlement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636E424A-96C2-4F9B-AF2F-C07B01A3A551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C6954F-37A8-4F8C-855E-BE88062258DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34452" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="88">
   <si>
     <t>MODEL</t>
   </si>
@@ -294,25 +294,28 @@
   </si>
   <si>
     <t>Reference</t>
+  </si>
+  <si>
+    <t>Share of total expenditures|Urban</t>
+  </si>
+  <si>
+    <t>Share of total expenditures|Rural</t>
+  </si>
+  <si>
+    <t>Share of total national expenditures by urban or rural population. Urban + Rural should sum to 100%.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -648,13 +651,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultColWidth="10.9296875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="50.7265625" customWidth="1"/>
+    <col min="4" max="4" width="50.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,7 +680,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -694,7 +697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -711,7 +714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -728,7 +731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -745,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -762,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -779,7 +782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -796,7 +799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -813,7 +816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -830,7 +833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -847,7 +850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -864,7 +867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -881,7 +884,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -898,7 +901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -915,7 +918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -932,7 +935,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -949,7 +952,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -966,7 +969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -983,7 +986,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1102,7 +1105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1119,7 +1122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1153,7 +1156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1204,7 +1207,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1238,7 +1241,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -1289,7 +1292,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -1306,7 +1309,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1323,7 +1326,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -1340,7 +1343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -1357,7 +1360,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -1391,7 +1394,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1425,7 +1428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -1442,7 +1445,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1459,7 +1462,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -1493,9 +1496,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
         <v>84</v>
@@ -1510,9 +1513,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B51" t="s">
         <v>84</v>
@@ -1527,49 +1530,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
         <v>84</v>
       </c>
       <c r="D52" t="s">
+        <v>85</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" t="s">
         <v>77</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53" t="s">
-        <v>79</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
-      </c>
-      <c r="D54" t="s">
-        <v>80</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -1578,7 +1581,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -1595,7 +1598,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>84</v>
       </c>
       <c r="D56" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -1612,7 +1615,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1620,12 +1623,46 @@
         <v>84</v>
       </c>
       <c r="D57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" t="s">
         <v>83</v>
       </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
         <v>78</v>
       </c>
     </row>
